--- a/RUNBOOK-48-test-questions.xlsx
+++ b/RUNBOOK-48-test-questions.xlsx
@@ -704,22 +704,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>谁在消费 marketing-cm_sms 这个 topic？</t>
+          <t>谁在消费 marketing 的 CM SMS topic？</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>consumers(destination="cm_sms" 或完整 topic)</t>
+          <t>consumers(destination="&lt;完整 marketing-cm_sms topic&gt;")</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>message_edges 里消费该 destination 的仓库列表</t>
+          <t>消费该 destination 的仓库列表。别用裸 "cm_sms" 子串——它同时匹配 marketing + servicing 两个 destination(内网实测);用 message_edges.csv 里完整的 marketing topic</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>消息图下游查询;注意子串匹配范围</t>
+          <t>消息图下游查询;子串匹配会撞两个 destination</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr"/>
@@ -748,22 +748,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>谁往 cm_sms topic 发消息？</t>
+          <t>谁往 2way SMS reply topic 发消息？</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>producers(destination="cm_sms")</t>
+          <t>producers(destination="hrn.hase.shared.notification.2way_sms_reply")</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>生产/发送到该 destination 的仓库列表</t>
+          <t>有真实 producer 的仓库列表(非空)。注意:producers(destination="cm_sms") 内网返回 0,是个假冒烟;Codex 实测 2way_sms_reply 有真实 producer</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>消息图上游查询</t>
+          <t>消息图上游查询;避免用返回 0 的 destination</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
@@ -836,22 +836,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>use case &lt;任一真实ID&gt; 走哪个 topic？</t>
+          <t>use case K3002 走哪个 topic？</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>usecase_route(use_case_id="&lt;真实ID&gt;")</t>
+          <t>usecase_route(use_case_id="K3002")</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>该 UC 的 topic(s),并声明这是 dev/SCT 快照、非生产</t>
+          <t>该 UC 的 topic(s) + dev/SCT 快照、非生产声明。用 K3002(Codex 实测在 dev/SCT 路由快照里)。另跑两分支:topic-only(按 topic 搜 UC)、pair 校验(两参数都传)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>验证 dev/SCT 免责声明;别与 use_cases_for_topic 混淆</t>
+          <t>验证 dev/SCT 免责声明 + usecase_route 的三种分支</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
@@ -880,22 +880,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>如果 &lt;某完整topic&gt; 变了，还有哪些 use case 受影响？</t>
+          <t>如果 &lt;某topic&gt; 变了，还有哪些 use case 受影响？</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>use_cases_for_topic(topic="&lt;完整topic&gt;", exact=true)</t>
+          <t>use_cases_for_topic(topic="&lt;topic&gt;", exact=false)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>全部路由到它的 UC + total;truncated 时说明还有多少;绝不把「快照里没有」说成「不存在」</t>
+          <t>全部路由到它的 UC + total;**用 marketing-batch topic(~69 条,Codex)配小 limit 强制 truncated=true**,确认答案说清还有多少;绝不把「快照里没有」说成「不存在」;别误加 use_case_id。另跑一条 exact=true 完整 topic</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>不谎报完整性 + 不误加 use_case_id 过滤(会隐藏兄弟)</t>
+          <t>强制截断路径 + 不谎报完整性</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>带行号的源码片段</t>
+          <t>带行号的源码片段。**另测越界防护**(此前没真测):read_file(path="../AGENTS.md") 必须被拒(path escapes mirror),不能读出来</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>冒烟:读文件 + mirror 越界防护</t>
+          <t>冒烟:读文件 + 真正验证 mirror 越界防护</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
@@ -1056,22 +1056,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>&lt;任一真实use_case_id&gt; 的完整消息流是怎样的？</t>
+          <t>use case K3002 的完整消息流是怎样的？</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>trace(use_case_id="&lt;真实ID&gt;")</t>
+          <t>trace(use_case_id="K3002")</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>沿异步消息线拼出的端到端流</t>
+          <t>沿异步消息线拼出的端到端流。另跑 destination 路径(trace(destination="&lt;topic&gt;"))和 unknown/partial 路径(乱码 id → 诚实说没找到/partial,不编造流)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>冒烟:trace 拼接是否正常</t>
+          <t>冒烟:trace 拼接 + 空/异常输入不编造</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr"/>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>callers.available=**true**,真实跨仓库调用方 + 依赖 + 消息 peer,每个调用方 cite 到 file:line</t>
+          <t>PASS = callers.available=true + 真实跨仓库调用方 cite 到 file:line。**别同时要求 deps+message**:Codex 实测 IngressService 的 resolved_repo=None、依赖/消息段为空;把空 deps 记为单独待查(符号→repo 解析缺陷),不算冒烟失败</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>⭐CodeGraph 命中路径:真实调用图(不是文本匹配)</t>
+          <t>⭐CodeGraph 命中路径;预期拆开,不过度断言</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
@@ -1225,9 +1225,9 @@
           <t>call_graph</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>🟢 冒烟</t>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>🔻 降级</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>路由到定义它的 bundle 的原始 explore 输出</t>
+          <t>路由到定义它的 bundle 的原始 explore 输出。**另跑两条降级路径**(同 T12b/c):未索引仓库符号 + CLI 缺失;确认降级时诚实,不吐一个看着权威的裸 dump</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>同 T12a/b/c 的三种风险;裸 dump 降级更不易被察觉</t>
+          <t>补未索引/CLI 缺失降级(之前只有成功路径)</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr"/>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>内嵌架构图,SMS 链高亮 + 文字说明受影响路径</t>
+          <t>内嵌架构图,SMS 链高亮 + 文字说明。**另补另外两种 kind**(source-system=PEGA 见 R47 #13):vendor("Sinch 出问题了"→kind=vendor,value=sinch)、use-case(kind=use-case,value=K3002)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>渠道 outage 变体(PEGA 接入点见 RUNBOOK-47 #13)</t>
+          <t>补 vendor / use-case 两种 kind</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr"/>
@@ -1452,17 +1452,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>&lt;任一真实use_case_id&gt; 是什么？渠道/上游/owner？</t>
+          <t>use case K3002 是什么？渠道/上游/owner？</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>usecase_impact(use_case_id="&lt;真实ID&gt;")</t>
+          <t>usecase_impact(use_case_id="K3002")</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>全貌:身份/渠道(channels_declared)/上游/owner/rule_text AST;AST 的 semantics=unconfirmed 时**不能当成已断言的 fallback 顺序**</t>
+          <t>全貌:身份/渠道(channels_declared)/上游/owner/rule_text AST。用 K3002(Codex 实测在 UAT 主数据里且能真正覆盖 rule_text_ast.semantics=unconfirmed;M2050 覆盖不全)。semantics=unconfirmed 时**不能当成已断言的 fallback 顺序**</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1751,12 +1751,20 @@
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>5. &lt;真实ID&gt;/&lt;完整topic&gt;/&lt;未索引仓库的类&gt; 这类占位,内网用真实数据替换后执行;找「未索引仓库的类」的步骤见 runbook Part B。</t>
+          <t>5. 前置条件:T17-T20(use case 工具)跑之前先设 $env:SDLC_USECASE_DATASET="index/usecase-snapshots/uat/20260720-1730" 并重启,否则会不可用/错误降级(见 runbook Part 0.3)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>6. K3002 是 Codex 实测可用的固定 use_case_id(同时在 UAT 主数据和 dev/SCT 快照里,能覆盖 rule_text AST);&lt;完整topic&gt;/&lt;未索引仓库的类&gt; 这类占位内网用真实数据替换,找靶子步骤见 runbook Part B(用 manifest 的 staged_repos,备选靶子 SapiAutoScanConfig)。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A16:H16"/>

--- a/RUNBOOK-48-test-questions.xlsx
+++ b/RUNBOOK-48-test-questions.xlsx
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1610,6 +1610,270 @@
         </is>
       </c>
     </row>
+    <row r="25" ht="62" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>T22</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>DB catalog(当前无工具)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ 能力边界</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>MDC 的数据库现在一共有多少张表？</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>应查询 live DB 的只读 catalog/schema(当前工具集里没有这个工具);现阶段只能辅助检查 UAT snapshot manifest + 离线数据库设计摘录</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>当前无法权威回答 live MDC database 的表总数,不能猜。可证明的只有:1) UAT snapshot 20260720-1730 实际导出 3 张表:tbl_use_case(2,810 行)、tbl_use_case_channel_rule(6,217 行)、tbl_use_case_ext(2,660 行);2) 离线数据库设计摘录列出 8 张 use-case 相关表。「导出 3 张」和「设计列 8 张」都≠整个 live MDC DB 的表总数。要真实答案须 DBA 提供只读 schema/catalog 导出(如 information_schema.tables 结果)或开放只读 DB catalog 工具。</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>禁止把 UAT 快照的 3 张表、设计文档的 8 张表、或 Java @Table 类数量冒充 live DB 总表数。证据:index/usecase-snapshots/uat/20260720-1730/manifest.json;.tmp/use_case_db_design_tables.md</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="62" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>T23</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>source_system_impact + UAT snapshot</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ 口径边界</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>MDC 现在有多少 use cases？HASE 和 non-HASE 各多少？</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>source_system_impact(source_system="MDC") + 对 UAT tbl_use_case.snapshot.csv 按 group_member 统计(source_system 大小写归一)</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>按 UAT snapshot 20260720-1730 的 total 口径:MDC 共 880 个 use cases;HASE 819;non-HASE 61。non-HASE 的 61 = HSBC 56 + group_member 空白/未知 5,不能把这 5 条未填写记录静默算成 HSBC。若只数当前 active:总数 876;HASE 817;non-HASE 59(HSBC 56 + 空白/未知 3);另有 inactive 4。回答必须同时写明 snapshot 时间与 total/active 口径。★口径说明:此处「MDC」按整个消息平台(tbl_use_case 全量)理解,用 source_system_impact(source_system="MDC") 取平台总数;若把 MDC 当成 source_system 字段值之一(MDC/PEGA/eAlert…)则数字含义不同——回答须说明用的是哪一种读法。</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>source_system_impact 可直接证明 MDC total=880、active=876、inactive=4;HASE/HSBC/空白拆分来自 UAT tbl_use_case 正式字段 group_member。证据:index/usecase-snapshots/uat/20260720-1730/tbl_use_case.snapshot.csv;.tmp/use_case_db_design_tables.md(group_member 示例值 HASE)</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="62" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>T24</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>list_repos + search_code/read_file</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ 术语消歧</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>请列出与 SMS feedback status 相关的 repo。</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>list_repos(query="feedback") + list_repos(query="tracking") + list_repos(channel="sms") + scoped search_code/read_file</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>必须先澄清「feedback status」含义:A. 若指客户点击/行为反馈:名称检索到 mc-hk-hase-email-feedback-api、mc-hk-hase-feedback-api、mc-hk-hase-wsb-feedback-api,但代码显示它们分别偏 Email、In-app/Push、WSB In-app,并非 SMS 投递回执主链。B. 若指 SMS 发送/投递状态(更贴合本题):核心 repos 应分层列出——状态 API:mc-hk-hase-htcl-tracking-api、amet-mdc-hsbc-cm-tracking-api;共享调用/配置:mc-hk-hase-api-rest-invoker、mc-hk-hase-api-starter;实际 tracking jobs:mc-hk-hase-svc-rt-gen-tracking-job、mc-hk-hase-svc-bat-tracking-job、mc-hk-hase-ssvc-bat-tracking-job。不能把搜到的全部 36 个 tracking 或 70 个 SMS 仓库不加区分当答案。</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>成功证据应含真实接口/配置:HTCL /v4/query-sms-status(含 /otp);CM POST /api/sms-status;api-starter 的 querySmsStatus 下游 URL;tracking job 里 Htcl/Csl/Cm/Lx SMS tracker 类。代码位置示例:mirror/mc-hk-hase-api-starter/src/main/resources/application-downstream-prod.yaml:256-286;CmStatusTrackingResource.java:29</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="62" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>T25</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>list_repos + search_code/read_file</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ 深度逻辑</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>需要检查 PN 的 opt-in status;请给出 repo 并总结 Push Notification opt-in 逻辑。</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>list_repos(query="preference") + scoped search_code(PushMessageValidator/AlertTypeEnum/PreferenceResource) + read_file</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>「opin」按上下文应理解为 opt-in。核心 repos:Preference 入口/资料维护:mc-hk-hase-preferences-api、mc-hk-hase-preferences-job;发送前把关:mc-hk-hase-api-dispatch-core、mc-hk-hase-api-delivery-core;共享支持:mc-hk-hase-api-rest-invoker、mc-hk-hase-api-common、mc-hk-hase-api-domain。逻辑:1) verifyPushPoint=false 时跳过检查;2) 必须找到客户资料;3) 必须有 device token,delivery-core 还把「NA」视为无 token;4) 必须有 Use Case 配置和客户 subscription list;5) Use Case 哪个 Push opt-in flag 为 Y,就必须在客户 subscription 找到同一 alertType 且 alertChannelStatus03=Y;6) 不满足即抛 NotOptInException 阻止继续发送。覆盖普通、高风险、Marketing、Credit Card 00507、Investment 99998、Securities 等 Push;delivery-core 还含 Marketing Insight。注意:opt-in 只证明「允许/有资格发送」,不证明消息实际已送达。</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>关键证据:preferences-api PreferenceResource.java:38-62;preferences-job DaascProcessService.java:133-145,256-332;api-dispatch-core PushMessageValidator.java:30-119;api-delivery-core PushMessageValidator.java:33-128;rest-invoker 的 CreatePnPreferenceInvoker(POST)/UpdatePnPreferenceInvoker(PUT)</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="62" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>T26</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>list_repos + 消息图(producers/consumers)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>🟢 消息图</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>请列出与 2-way SMS 相关的 repo。</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>list_repos(query="2way") + producers/consumers(destination="hrn.hase.shared.notification.2way_sms_reply") + repo_routes + scoped source search</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>不能只回答名称里带 2way 的那 1 个仓库;完整主链按职责列出——发出 2-way SMS:mc-hk-hase-svc-rt-hr-htcl-2way-sms-deli-job;接收客户回复:mc-hk-hase-hutchison-inbound-gateway;消费回复/对账报表:mc-hk-hase-reconciliation-report-job;查询投递状态:mc-hk-hase-svc-rt-hr-tracking-job(含 Htcl2WaySmsTracker / Htcl2WaySmsPollTracker);共享业务库:mc-hk-hase-api-delivery-core、mc-hk-hase-api-tracking-core、mc-hk-hase-api-dao、mc-hk-hase-api-domain、mc-hk-hase-api-rest-invoker(含 ReplyFraudFeedbackInvoker)。</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>消息图证据:reply topic「hrn.hase.shared.notification.2way_sms_reply」的 producer=mc-hk-hase-hutchison-inbound-gateway、consumer=mc-hk-hase-reconciliation-report-job(index/message_edges.csv:206);outbound delivery topic 边在 index/message_edges.csv:385。list_repos(query="2way") 只返回 1 个命名撞中的仓库,不代表主链只有 1 个 repo。</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="62" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>T27</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>list_repos + repo_routes + search_code</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ 渠道边界</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>WeChat 用的是 personal chat channel 还是 company WeChat channel？</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>list_repos(channel="wechat") + repo_routes + scoped search_code(openid/template_id/corpId/agentId/qyapi.weixin.qq.com)</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>现有代码最符合「腾讯微信公众号(Official Account)」模板消息,不是个人对个人的 peer-to-peer chat;同时也没有证据表明是企业微信/WeCom。证据特征:按用户 openid 发送、用 appid/appsecret + access token、调 /cgi-bin/message/template/send、请求体字段 touser/template_id/data。相关 delivery repos 只有 2 个:mc-hk-hase-ssvc-rt-gen-wechat-deli-job(realtime general)、mc-hk-hase-ssvc-rt-hr-wechat-deli-job(realtime high-risk),两者差异是 general/high-risk,不是 personal/company。代码里未见企业微信常见的 corpId、agentId 或 qyapi.weixin.qq.com。</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>关键证据:api-starter application-downstream.yaml:591-595;SendWeChatMessageRequest.java:29-33;WeChatService.java:86-125;TencentWechatRouter.java:54-84,110-133。回答时别把「向个人 openid 发公众号消息」误写成「个人聊天」,也别把公众号误写成企业微信。</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1622,7 +1886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1694,22 +1958,33 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>已判定 PASS</t>
+          <t>已判定 PASS(含 T22–T27)</t>
         </is>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIF(全工具冒烟!J2:J24,"PASS")</f>
+        <f>COUNTIF(全工具冒烟!J2:J30,"PASS")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>已判定 FAIL</t>
+          <t>已判定 FAIL(含 T22–T27)</t>
         </is>
       </c>
       <c r="B9" s="11">
-        <f>COUNTIF(全工具冒烟!J2:J24,"FAIL")</f>
+        <f>COUNTIF(全工具冒烟!J2:J30,"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>领导追加业务问题(T22–T27,跨工具 Q&amp;A)</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>COUNTA(全工具冒烟!A25:A30)</f>
         <v/>
       </c>
     </row>
@@ -1759,6 +2034,13 @@
       <c r="A18" s="13" t="inlineStr">
         <is>
           <t>6. K3002 是 Codex 实测可用的固定 use_case_id(同时在 UAT 主数据和 dev/SCT 快照里,能覆盖 rule_text AST);&lt;完整topic&gt;/&lt;未索引仓库的类&gt; 这类占位内网用真实数据替换,找靶子步骤见 runbook Part B(用 manifest 的 staged_repos,备选靶子 SapiAutoScanConfig)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>7. T22–T27 是业务方/领导会议追加的跨工具业务问题(不是单工具冒烟):T22 测「没有只读 DB catalog 工具」的能力边界,T23 走 source_system_impact + UAT 快照口径,T24–T27 组合 list_repos / search_code / read_file / 消息图 / repo_routes。类型标签(能力边界/口径边界/术语消歧/深度逻辑/消息图/渠道边界)是问题类别,不是冒烟图例;它们不影响 runbook Part C 的 21==21 工具覆盖不变量。</t>
         </is>
       </c>
     </row>
